--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A08EBC-6D50-420E-AE2B-C151CCC4B4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79560B0F-5916-4B49-BA7B-4F755BA257C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="435" yWindow="-15015" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8340" yWindow="-12975" windowWidth="15525" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -89,6 +89,47 @@
   </si>
   <si>
     <t>effectID[]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP10回復</t>
+    <rPh sb="4" eb="6">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度50HP10回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度100回復</t>
+    <rPh sb="6" eb="8">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロア全体</t>
+    <rPh sb="3" eb="5">
+      <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部屋全体</t>
+    <rPh sb="0" eb="2">
+      <t>ヘヤ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンタイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -437,11 +478,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
@@ -511,17 +552,21 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-1</v>
+      </c>
       <c r="D3" s="2">
         <f>VLOOKUP(E3,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>-1</v>
@@ -537,20 +582,24 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-1</v>
+      </c>
       <c r="D4" s="2">
         <f>VLOOKUP(E4,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2">
         <v>-1</v>
@@ -563,25 +612,133 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-1</v>
+      </c>
       <c r="D5" s="2">
         <f>VLOOKUP(E5,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
+        <f>VLOOKUP(E6,reference!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="F6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2">
+        <f>VLOOKUP(E7,reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
+        <f>VLOOKUP(E8,reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
+        <f>VLOOKUP(E9,reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -596,7 +753,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E5</xm:sqref>
+          <xm:sqref>E2:E9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -606,7 +763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7B5D92-8AB0-4E58-AB32-5914247D4A74}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
@@ -637,6 +794,22 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79560B0F-5916-4B49-BA7B-4F755BA257C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22836762-4AED-4D64-A5AF-D85D04ACF61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="-12975" windowWidth="15525" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="-14970" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -129,6 +129,20 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部屋内50ダメージ</t>
+    <rPh sb="0" eb="3">
+      <t>ヘヤナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部屋内31ダメージ</t>
+    <rPh sb="0" eb="3">
+      <t>ヘヤナイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -642,17 +656,21 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-1</v>
+      </c>
       <c r="D6" s="2">
         <f>VLOOKUP(E6,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2">
         <v>-1</v>
@@ -668,17 +686,21 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-1</v>
+      </c>
       <c r="D7" s="2">
         <f>VLOOKUP(E7,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7" s="2">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22836762-4AED-4D64-A5AF-D85D04ACF61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC9135E-8556-4080-9DA0-8F94EC88828C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="-14970" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8745" yWindow="-14475" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -143,6 +143,20 @@
     <t>部屋内31ダメージ</t>
     <rPh sb="0" eb="3">
       <t>ヘヤナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5ダメ+アイテム焼き</t>
+    <rPh sb="8" eb="9">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを腐らせる</t>
+    <rPh sb="5" eb="6">
+      <t>クサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -716,8 +730,12 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4001</v>
+      </c>
       <c r="D8" s="2">
         <f>VLOOKUP(E8,reference!A:B,2,FALSE)</f>
         <v>0</v>
@@ -726,10 +744,10 @@
         <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2">
         <v>-1</v>
@@ -742,8 +760,12 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4002</v>
+      </c>
       <c r="D9" s="2">
         <f>VLOOKUP(E9,reference!A:B,2,FALSE)</f>
         <v>0</v>
@@ -752,7 +774,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G9" s="2">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC9135E-8556-4080-9DA0-8F94EC88828C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C0291F-5BA8-4C8D-8DE8-F5F3D797A0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8745" yWindow="-14475" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2235" yWindow="-14370" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -158,6 +158,40 @@
     <rPh sb="5" eb="6">
       <t>クサ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前方10マス場所替え</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンポウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前方10マス25ダメ</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンポウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10マス吹き飛ばし</t>
+    <rPh sb="4" eb="5">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前方10ワープ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -506,14 +540,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -783,6 +817,126 @@
         <v>-1</v>
       </c>
       <c r="I9" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D10" s="2">
+        <f>VLOOKUP(E10,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2">
+        <v>9</v>
+      </c>
+      <c r="G10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="2">
+        <f>VLOOKUP(E11,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D12" s="2">
+        <f>VLOOKUP(E12,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="2">
+        <f>VLOOKUP(E13,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2">
+        <v>12</v>
+      </c>
+      <c r="G13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -797,7 +951,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E9</xm:sqref>
+          <xm:sqref>E2:E13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C0291F-5BA8-4C8D-8DE8-F5F3D797A0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F2A4CB-D852-4781-AC4E-B58C5847F867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="-14370" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="-13800" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -192,6 +192,34 @@
   </si>
   <si>
     <t>前方10ワープ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起点と周囲８マス</t>
+    <rPh sb="0" eb="2">
+      <t>キテン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>罠を可視化</t>
+    <rPh sb="0" eb="1">
+      <t>ワナ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カシカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -540,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -940,6 +968,126 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D14" s="2">
+        <f>VLOOKUP(E14,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="2">
+        <f>VLOOKUP(E15,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D16" s="2">
+        <f>VLOOKUP(E16,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D17" s="2">
+        <f>VLOOKUP(E17,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="2">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -951,7 +1099,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E13</xm:sqref>
+          <xm:sqref>E2:E17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -961,10 +1109,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7B5D92-8AB0-4E58-AB32-5914247D4A74}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1008,6 +1156,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F2A4CB-D852-4781-AC4E-B58C5847F867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914CE1BF-1035-41AE-99D9-34FBDE333862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="-13800" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14250" yWindow="-13320" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -116,13 +116,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>フロア全体</t>
-    <rPh sb="3" eb="5">
-      <t>ゼンタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部屋全体</t>
     <rPh sb="0" eb="2">
       <t>ヘヤ</t>
@@ -219,6 +212,32 @@
     </rPh>
     <rPh sb="2" eb="5">
       <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起点と周囲8に50%爆発</t>
+    <rPh sb="0" eb="2">
+      <t>キテン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起点と周囲8に100%爆発</t>
+    <rPh sb="0" eb="2">
+      <t>キテン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -568,11 +587,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
@@ -733,7 +752,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2">
         <v>-1</v>
@@ -743,7 +762,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
         <v>4</v>
@@ -763,7 +782,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2">
         <v>-1</v>
@@ -773,7 +792,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2">
         <v>5</v>
@@ -793,7 +812,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2">
         <v>4001</v>
@@ -823,7 +842,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2">
         <v>4002</v>
@@ -853,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2">
         <v>-1</v>
@@ -883,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2">
         <v>-1</v>
@@ -913,7 +932,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2">
         <v>-1</v>
@@ -943,7 +962,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2">
         <v>-1</v>
@@ -973,7 +992,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2">
         <v>-1</v>
@@ -1003,7 +1022,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2">
         <v>-1</v>
@@ -1033,7 +1052,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2">
         <v>-1</v>
@@ -1063,7 +1082,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2">
         <v>-1</v>
@@ -1085,6 +1104,66 @@
         <v>-1</v>
       </c>
       <c r="I17" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D18" s="2">
+        <f>VLOOKUP(E18,reference!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="2">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="2">
+        <f>VLOOKUP(E19,reference!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1099,7 +1178,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E17</xm:sqref>
+          <xm:sqref>E2:E19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1109,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7B5D92-8AB0-4E58-AB32-5914247D4A74}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
@@ -1142,7 +1221,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1150,18 +1229,10 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
